--- a/Jira/Plan de Prueba para Jira_y_Reportes de Bug/Modulo_Seguridad de Acceso/Reporte de  Bugs_Test Cases_Seguridad de Acceso -v 3.0.xlsx
+++ b/Jira/Plan de Prueba para Jira_y_Reportes de Bug/Modulo_Seguridad de Acceso/Reporte de  Bugs_Test Cases_Seguridad de Acceso -v 3.0.xlsx
@@ -5,11 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Portafolio\Plan de Prueba para Jira_y_Reportes de Bug\Modulo_Seguridad de Acceso\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Portafolio\Jira\Plan de Prueba para Jira_y_Reportes de Bug\Modulo_Seguridad de Acceso\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="pVBMFF48OHvE8+G2taKZwfVDWIIKIkc7knDzeCggczzvjw/IYgweKGPM1Ps55o+Q5xBirnWQcPIbT49HKbp8IA==" workbookSaltValue="WdDm9L+iveTB1hBdLcq/OQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases -v 3.0" sheetId="3" r:id="rId1"/>
@@ -1257,6 +1258,7 @@
       <c r="G14" s="38"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="AeT1mW7W/GEx7HCgwOdiPQq4/ULGc4FEoj+nnZUrF2opVfztw8hkEkmrV3bZnruyu7CerFy3Hy3jVDFE4sRAFg==" saltValue="uF1DcXxcVLYjjta1QoN5Pg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -1462,6 +1464,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="2IWNy/5ym/Ba01aX0eMYx7BNRQ0TIWZ+KM5IcG1dxp16bKwYD3tsfcC82XTZtzHB9lRgo1iNMMncs9S/cX+0qg==" saltValue="x+S8Wulb2iq9JGtiuSUENA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
@@ -1670,6 +1673,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="qzFO5kt+2PAN4OmIyUsobPci4VqEs8nzaOcQdCCfG1/qZPDoD3ZYGyImj8izBPw2+bQtSKg1WaWR2SAXW3mCmQ==" saltValue="Vx63JdfJZhwOAhAEj0s2mw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
